--- a/docs/03_test/testcase.xlsx
+++ b/docs/03_test/testcase.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FE062A-FED4-44BE-BC75-113077038828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F368AC-9775-47F3-95AD-889AC9A49B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{33168205-4D20-40BB-B12D-A9B404AB5FFC}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{33168205-4D20-40BB-B12D-A9B404AB5FFC}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="社員登録" sheetId="4" r:id="rId1"/>
+    <sheet name="部署登録" sheetId="3" r:id="rId2"/>
+    <sheet name="一覧" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="62">
   <si>
     <t>テストケース</t>
     <phoneticPr fontId="1"/>
@@ -517,16 +519,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>メールアドレスに全角が含まれている</t>
-    <rPh sb="8" eb="10">
-      <t>ゼンカク</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>フク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>半角のみで入力してくださいと表示</t>
     <rPh sb="0" eb="2">
       <t>ハンカク</t>
@@ -642,117 +634,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>社員数9999人の状態で登録ボタン押下</t>
-    <rPh sb="0" eb="2">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>スウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ニン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>社員数9998人の状態で登録ボタン押下</t>
-    <rPh sb="0" eb="2">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>スウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ニン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>部署数99個の状態で登録ボタン押下</t>
-    <rPh sb="0" eb="3">
-      <t>ブショスウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>部署数98個の状態で登録ボタン押下</t>
-    <rPh sb="0" eb="3">
-      <t>ブショスウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>部署数の上限ですと表示</t>
-    <rPh sb="0" eb="3">
-      <t>ブショスウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ジョウゲン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>社員数の上限ですと表示</t>
-    <rPh sb="0" eb="2">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>スウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ジョウゲン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>部署名が長すぎますと表示</t>
     <rPh sb="0" eb="3">
       <t>ブショメイ</t>
@@ -798,6 +679,80 @@
     <t>異常系</t>
     <rPh sb="0" eb="3">
       <t>イジョウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員登録完了画面でメニューに戻るボタン押下</t>
+    <rPh sb="0" eb="6">
+      <t>シャイントウロクカンリョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員登録完了画面で続けて登録ボタン押下</t>
+    <rPh sb="0" eb="6">
+      <t>シャイントウロクカンリョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレスが正しい形式でない</t>
+    <rPh sb="8" eb="9">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ケイシキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署一覧画面へ遷移</t>
+    <rPh sb="0" eb="2">
+      <t>ブショ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員登録</t>
+    <rPh sb="0" eb="4">
+      <t>シャイントウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署登録</t>
+    <rPh sb="0" eb="4">
+      <t>ブショトウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一覧</t>
+    <rPh sb="0" eb="2">
+      <t>イチラン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -908,12 +863,24 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -924,16 +891,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1269,6 +1227,1670 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5301FE7D-5A36-45F1-B735-02AF71F33A08}">
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="3" max="3" width="39.83203125" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="8"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="8"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="8"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="1">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="9">
+        <v>46168</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="9">
+        <v>46168</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="1">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="9">
+        <v>46168</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="1">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="9">
+        <v>46168</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="1">
+        <v>5</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="9">
+        <v>46168</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="1">
+        <v>6</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="9">
+        <v>46168</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="1">
+        <v>7</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="9">
+        <v>46168</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="1">
+        <v>8</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="9">
+        <v>46168</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="1">
+        <v>9</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="9">
+        <v>46168</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="1">
+        <v>10</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="9">
+        <v>46168</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="1">
+        <v>11</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="9">
+        <v>46168</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="1">
+        <v>12</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="9">
+        <v>46168</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="1">
+        <v>13</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="9">
+        <v>46168</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="1">
+        <v>14</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" s="9">
+        <v>46168</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="1">
+        <v>15</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="1">
+        <v>16</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="1">
+        <v>17</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="1">
+        <v>18</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="1">
+        <v>19</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="1">
+        <v>20</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="1">
+        <v>21</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="1">
+        <v>22</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="1">
+        <v>23</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="1">
+        <v>24</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="1">
+        <v>25</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="1">
+        <v>26</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="1">
+        <v>27</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="1">
+        <v>28</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="1">
+        <v>29</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="1">
+        <v>30</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="1">
+        <v>31</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="1">
+        <v>32</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="1">
+        <v>33</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="1">
+        <v>34</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="1">
+        <v>35</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="1">
+        <v>36</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="1">
+        <v>37</v>
+      </c>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="1">
+        <v>38</v>
+      </c>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="1">
+        <v>39</v>
+      </c>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="1">
+        <v>40</v>
+      </c>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="1">
+        <v>41</v>
+      </c>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="1">
+        <v>42</v>
+      </c>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="1">
+        <v>43</v>
+      </c>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="1">
+        <v>44</v>
+      </c>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="1">
+        <v>45</v>
+      </c>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="1">
+        <v>46</v>
+      </c>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="1">
+        <v>47</v>
+      </c>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="1">
+        <v>48</v>
+      </c>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="1">
+        <v>49</v>
+      </c>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="1">
+        <v>50</v>
+      </c>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="1">
+        <v>51</v>
+      </c>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="1">
+        <v>52</v>
+      </c>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="1">
+        <v>53</v>
+      </c>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="1">
+        <v>54</v>
+      </c>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="1">
+        <v>55</v>
+      </c>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="1">
+        <v>56</v>
+      </c>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="A4:G4"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{030557CD-228D-4485-8C9F-2DDC08CA0762}">
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="39.5" customWidth="1"/>
+    <col min="3" max="3" width="38.6640625" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="8"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="8"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="8"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="1">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="9">
+        <v>46169</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="9">
+        <v>46169</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="1">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="9">
+        <v>46169</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="1">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="9">
+        <v>46169</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="1">
+        <v>5</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="9">
+        <v>46169</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="1">
+        <v>6</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="9">
+        <v>46169</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="1">
+        <v>7</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="9">
+        <v>46169</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="1">
+        <v>8</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="9">
+        <v>46169</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="1">
+        <v>9</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="9">
+        <v>46169</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="1">
+        <v>10</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="9">
+        <v>46169</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="1">
+        <v>11</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="1">
+        <v>12</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="1">
+        <v>13</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="1">
+        <v>14</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="1">
+        <v>15</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="1">
+        <v>16</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="1">
+        <v>17</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="1">
+        <v>18</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="1">
+        <v>19</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="1">
+        <v>20</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="1">
+        <v>21</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="1">
+        <v>22</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="1">
+        <v>23</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="1">
+        <v>24</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="1">
+        <v>25</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="1">
+        <v>26</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="1">
+        <v>27</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="1">
+        <v>28</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="1">
+        <v>29</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="1">
+        <v>30</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="1">
+        <v>31</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="1">
+        <v>32</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="1">
+        <v>33</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="1">
+        <v>34</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="1">
+        <v>35</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="1">
+        <v>36</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="1">
+        <v>37</v>
+      </c>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="1">
+        <v>38</v>
+      </c>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="1">
+        <v>39</v>
+      </c>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="1">
+        <v>40</v>
+      </c>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="1">
+        <v>41</v>
+      </c>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="1">
+        <v>42</v>
+      </c>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="1">
+        <v>43</v>
+      </c>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="1">
+        <v>44</v>
+      </c>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="1">
+        <v>45</v>
+      </c>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="1">
+        <v>46</v>
+      </c>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="1">
+        <v>47</v>
+      </c>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="1">
+        <v>48</v>
+      </c>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="1">
+        <v>49</v>
+      </c>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="1">
+        <v>50</v>
+      </c>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="1">
+        <v>51</v>
+      </c>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="1">
+        <v>52</v>
+      </c>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="1">
+        <v>53</v>
+      </c>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="1">
+        <v>54</v>
+      </c>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="1">
+        <v>55</v>
+      </c>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="1">
+        <v>56</v>
+      </c>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="A4:G4"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC1010E-FCCC-44C4-A6A2-EFACD3967C9B}">
   <dimension ref="A1:G61"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -1280,50 +2902,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="8"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="8"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
@@ -1353,13 +2977,17 @@
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="9">
+        <v>46169</v>
+      </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
         <v>40</v>
@@ -1370,16 +2998,20 @@
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="9">
+        <v>46169</v>
+      </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1387,16 +3019,20 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+        <v>57</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="9">
+        <v>46169</v>
+      </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1404,425 +3040,285 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="9">
+        <v>46169</v>
+      </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1">
         <v>5</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1">
         <v>6</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1">
         <v>7</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1">
         <v>8</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="G13" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1">
         <v>9</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1">
         <v>10</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-      <c r="G15" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1">
         <v>11</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
-      <c r="G16" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1">
         <v>12</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
-      <c r="G17" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1">
         <v>13</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1">
         <v>14</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
-      <c r="G19" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1">
         <v>15</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
-      <c r="G20" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1">
         <v>16</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
-      <c r="G21" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1">
         <v>17</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
-      <c r="G22" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="G22" s="1"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1">
         <v>18</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>42</v>
-      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
-      <c r="G23" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1">
         <v>19</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
-      <c r="G24" s="1" t="s">
-        <v>58</v>
-      </c>
+      <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1">
         <v>20</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
-      <c r="G25" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1">
         <v>21</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
-      <c r="G26" s="1" t="s">
-        <v>58</v>
-      </c>
+      <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1">
         <v>22</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>56</v>
-      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
-      <c r="G27" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1">
         <v>23</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
-      <c r="G28" s="1" t="s">
-        <v>58</v>
-      </c>
+      <c r="G28" s="1"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1">
         <v>24</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>55</v>
-      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
-      <c r="G29" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1">
         <v>25</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
-      <c r="G30" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="1">
         <v>26</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
-      <c r="G31" s="1" t="s">
-        <v>58</v>
-      </c>
+      <c r="G31" s="1"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="1">
         <v>27</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
-      <c r="G32" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="G32" s="1"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="1">
         <v>28</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
-      <c r="G33" s="1" t="s">
-        <v>58</v>
-      </c>
+      <c r="G33" s="1"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="1">
@@ -2147,15 +3643,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100F53224CB4AB7E84C876E95102DDD2B7D" ma:contentTypeVersion="1" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="947de67177af69f3fd6a28854a415f99">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="35ae0af6-260d-49f6-9ae2-0fef1c1b6caa" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="21359be01a8b63129af408f5f6c8fbf0" ns3:_="">
     <xsd:import namespace="35ae0af6-260d-49f6-9ae2-0fef1c1b6caa"/>
@@ -2281,21 +3768,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A8C5614-04C3-47D2-A125-2982C6BC1E1E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3D5552C-3D96-467E-A4EE-B2A4F00FB571}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2313,7 +3801,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4D04206-A8F8-45E7-81AB-0BC91D8EB202}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -2327,4 +3815,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A8C5614-04C3-47D2-A125-2982C6BC1E1E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>